--- a/esyluban/examples/dev/DataTables/mail/邮箱系统数据表.xlsx
+++ b/esyluban/examples/dev/DataTables/mail/邮箱系统数据表.xlsx
@@ -1114,7 +1114,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
